--- a/data-manipulation-scripts/sheets-cleanup/sheets/PEDAL - 24_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/PEDAL - 24_01.xlsx
@@ -58,7 +58,7 @@
     <t>PEDALEIRA TRASEIRA SMARTFOX YBR125 2008/ XTZ125</t>
   </si>
   <si>
-    <t xml:space="preserve">PEDALEIRA TRASEIRA OSI TITAN FILTRO AR DO HUSDSONN160 </t>
+    <t xml:space="preserve">PEDALEIRA TRASEIRA OSI TITAN160 </t>
   </si>
   <si>
     <t>PEDALEIRA TRASEIRA IRON TITAN FAN160</t>
@@ -440,7 +440,9 @@
       <c r="C5" s="2">
         <v>2.0</v>
       </c>
-      <c r="D5" s="5"/>
+      <c r="D5" s="2">
+        <v>80.0</v>
+      </c>
       <c r="E5" s="3" t="s">
         <v>7</v>
       </c>
@@ -455,7 +457,9 @@
       <c r="C6" s="2">
         <v>2.0</v>
       </c>
-      <c r="D6" s="5"/>
+      <c r="D6" s="2">
+        <v>40.0</v>
+      </c>
       <c r="E6" s="3" t="s">
         <v>7</v>
       </c>
@@ -468,7 +472,9 @@
       <c r="C7" s="2">
         <v>2.0</v>
       </c>
-      <c r="D7" s="5"/>
+      <c r="D7" s="2">
+        <v>30.0</v>
+      </c>
       <c r="E7" s="3" t="s">
         <v>7</v>
       </c>
@@ -481,7 +487,9 @@
       <c r="C8" s="2">
         <v>1.0</v>
       </c>
-      <c r="D8" s="5"/>
+      <c r="D8" s="2">
+        <v>30.0</v>
+      </c>
       <c r="E8" s="3" t="s">
         <v>7</v>
       </c>
@@ -494,7 +502,9 @@
       <c r="C9" s="2">
         <v>2.0</v>
       </c>
-      <c r="D9" s="5"/>
+      <c r="D9" s="2">
+        <v>30.0</v>
+      </c>
       <c r="E9" s="3" t="s">
         <v>7</v>
       </c>
@@ -509,7 +519,9 @@
       <c r="C10" s="2">
         <v>1.0</v>
       </c>
-      <c r="D10" s="5"/>
+      <c r="D10" s="2">
+        <v>30.0</v>
+      </c>
       <c r="E10" s="3" t="s">
         <v>7</v>
       </c>
@@ -522,7 +534,9 @@
       <c r="C11" s="2">
         <v>1.0</v>
       </c>
-      <c r="D11" s="5"/>
+      <c r="D11" s="2">
+        <v>35.0</v>
+      </c>
       <c r="E11" s="3" t="s">
         <v>7</v>
       </c>
